--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.34140954926634</v>
+        <v>3.46797905175578</v>
       </c>
       <c r="D2" t="n">
-        <v>21.31532705163741</v>
+        <v>3.46374064589108</v>
       </c>
       <c r="E2" t="n">
-        <v>5.920924027537088</v>
+        <v>0.9621501544747767</v>
       </c>
       <c r="F2" t="n">
-        <v>5.879891513881735</v>
+        <v>0.9554823710057821</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.58811985351075</v>
+        <v>5.458069476195498</v>
       </c>
       <c r="D3" t="n">
-        <v>32.95914204463042</v>
+        <v>5.355860582252443</v>
       </c>
       <c r="E3" t="n">
-        <v>5.920924027537088</v>
+        <v>0.9621501544747767</v>
       </c>
       <c r="F3" t="n">
-        <v>5.879891513881735</v>
+        <v>0.9554823710057821</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.36102706560976</v>
+        <v>5.096166898161586</v>
       </c>
       <c r="D4" t="n">
-        <v>31.23451513039936</v>
+        <v>5.075608708689896</v>
       </c>
       <c r="E4" t="n">
-        <v>5.920924027537088</v>
+        <v>0.9621501544747767</v>
       </c>
       <c r="F4" t="n">
-        <v>5.879891513881735</v>
+        <v>0.9554823710057821</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.49131881001868</v>
+        <v>6.092339306628036</v>
       </c>
       <c r="D5" t="n">
-        <v>37.4410008296521</v>
+        <v>6.084162634818467</v>
       </c>
       <c r="E5" t="n">
-        <v>5.920924027537088</v>
+        <v>0.9621501544747767</v>
       </c>
       <c r="F5" t="n">
-        <v>5.879891513881735</v>
+        <v>0.9554823710057821</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.37239528091704</v>
+        <v>6.073014233149019</v>
       </c>
       <c r="D6" t="n">
-        <v>37.2536912061866</v>
+        <v>6.053724821005323</v>
       </c>
       <c r="E6" t="n">
-        <v>5.920924027537088</v>
+        <v>0.9621501544747767</v>
       </c>
       <c r="F6" t="n">
-        <v>5.879891513881735</v>
+        <v>0.9554823710057821</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
